--- a/out/Attention-mamba2_repeat_2_000002.xlsx
+++ b/out/Attention-mamba2_repeat_2_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.228705708809412</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.2554444171274075</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.2554444171274075</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.2554444171274075</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.228705708809412</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.228705708809412</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.228705708809412</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.225252353036831</v>
+        <v>3.828705708809411</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.2554444171274075</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6252523530368312</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>2.418340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.818340913531692</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.8554444171274074</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_2_000002.xlsx
+++ b/out/Attention-mamba2_repeat_2_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.2212197045618354</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.818340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.818340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6252523530368312</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.418340913531692</v>
+        <v>0.9168981654917838</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.818340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>2.418340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.818340913531692</v>
+        <v>1.612576626421732</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.818340913531692</v>
+        <v>1.412576626421732</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.818340913531692</v>
+        <v>0.7168981654917838</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.225252353036831</v>
+        <v>0.02121970456183539</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.225252353036831</v>
+        <v>-0.674458756368113</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_2_000002.xlsx
+++ b/out/Attention-mamba2_repeat_2_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2029093950986862</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3450662791728973</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.265657365322113</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.1714596003293991</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.2473318427801132</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.2018321007490158</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1402530819177628</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.3051792979240417</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.4059036076068878</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.3216423392295837</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.1684734225273132</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.08943167328834534</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1799722015857697</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.1260575205087662</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.1012265980243683</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.1157293915748596</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.1430018246173859</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.1330499947071075</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.1035881042480469</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1108961626887321</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.1329854726791382</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.09884679317474365</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.08685801923274994</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.3805728852748871</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.3215166926383972</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2350302785634995</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2440267652273178</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.1989818513393402</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.123253770172596</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.1004741340875626</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.1223552003502846</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.08935345709323883</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.09268514811992645</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.111846387386322</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.1958319842815399</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.3785246610641479</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.3362975418567657</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.2237957119941711</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.3872865438461304</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.3846061229705811</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.1985444277524948</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0939415767788887</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0911637470126152</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.01742114126682281</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0369752012193203</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.04925280064344406</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.09719760715961456</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.06005785241723061</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.1299077272415161</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.05442016571760178</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.06444395333528519</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.16</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.07186150550842285</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.07350623607635498</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.07482249289751053</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.05305556207895279</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01055753603577614</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.06269669532775879</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.08061366528272629</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.08197681605815887</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.16</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.1108302623033524</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.06600624322891235</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.07610226422548294</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.16</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.07568160444498062</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.105487048625946</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.09019684046506882</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.06933597475290298</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.05440469831228256</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0867888405919075</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0707964226603508</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.068707175552845</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.05209867656230927</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0005612298846244812</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.674458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0384579598903656</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.2212197045618354</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.0004858933389186859</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.05870705842971802</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.05335518717765808</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.02700178325176239</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.612576626421732</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.04470343887805939</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.612576626421732</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.04987965524196625</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.612576626421732</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.04540020227432251</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.04811068624258041</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.007467985153198242</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.05457887053489685</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.04480016231536865</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.04498902708292007</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.412576626421732</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.05411030352115631</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0279642716050148</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.03396087884902954</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.05659492313861847</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.03630799055099487</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.03796381503343582</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.04701521992683411</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.04896462708711624</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.04587066173553467</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.612576626421732</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.05391864478588104</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.03807695955038071</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.04818764328956604</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9168981654917838</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.03586387634277344</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.612576626421732</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.05076360702514648</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.612576626421732</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.00429101288318634</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.05323886126279831</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.04348328709602356</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.02488206326961517</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.04688750207424164</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.03479583561420441</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.03747621178627014</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.612576626421732</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.04493261873722076</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.412576626421732</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.04749457538127899</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.412576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.04194782674312592</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.412576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.05188500136137009</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.412576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.0249738022685051</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.412576626421732</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.04779352247714996</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.412576626421732</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.03729608654975891</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.412576626421732</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.04784089326858521</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.412576626421732</v>
+        <v>-0.16</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.02761418372392654</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7168981654917838</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.08415214717388153</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.02121970456183539</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.09932079166173935</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02543231844902039</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.1033344939351082</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.04053862392902374</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.05571398138999939</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.03743407875299454</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.05488412827253342</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01704306527972221</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.1478634625673294</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.674458756368113</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_2_000002.xlsx
+++ b/out/Attention-mamba2_repeat_2_000002.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.2029093950986862</v>
+        <v>-0.2029209733009338</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3450662791728973</v>
+        <v>-0.345067024230957</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.265657365322113</v>
+        <v>-0.2656668126583099</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.1714596003293991</v>
+        <v>-0.1714734584093094</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.2473318427801132</v>
+        <v>-0.2473408132791519</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.2018321007490158</v>
+        <v>-0.2018439471721649</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1402530819177628</v>
+        <v>-0.1402698904275894</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.3051792979240417</v>
+        <v>-0.305175244808197</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.4059036076068878</v>
+        <v>-0.4058653116226196</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.3216423392295837</v>
+        <v>-0.3216405510902405</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.1684734225273132</v>
+        <v>-0.1685240119695663</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.08943167328834534</v>
+        <v>-0.0894438624382019</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1799722015857697</v>
+        <v>-0.1799680292606354</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.1260575205087662</v>
+        <v>-0.1260639429092407</v>
       </c>
       <c r="JB15" t="n">
         <v>0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.1012265980243683</v>
+        <v>-0.1012373715639114</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.1157293915748596</v>
+        <v>-0.1157386228442192</v>
       </c>
       <c r="JB17" t="n">
         <v>0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.1430018246173859</v>
+        <v>-0.1430062353610992</v>
       </c>
       <c r="JB18" t="n">
         <v>0.8599999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.1330499947071075</v>
+        <v>-0.1330553144216537</v>
       </c>
       <c r="JB19" t="n">
         <v>0.7199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.1035881042480469</v>
+        <v>-0.1035984307527542</v>
       </c>
       <c r="JB20" t="n">
         <v>0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1108961626887321</v>
+        <v>-0.1109056770801544</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.1329854726791382</v>
+        <v>-0.1329896450042725</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.09884679317474365</v>
+        <v>-0.09885669499635696</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.08685801923274994</v>
+        <v>-0.08687868714332581</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.3805728852748871</v>
+        <v>-0.3805267214775085</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.3215166926383972</v>
+        <v>-0.3214888870716095</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2350302785634995</v>
+        <v>-0.2350233793258667</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2440267652273178</v>
+        <v>-0.2440188229084015</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.1989818513393402</v>
+        <v>-0.1989771574735641</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.3</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.123253770172596</v>
+        <v>-0.1232592463493347</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.1004741340875626</v>
+        <v>-0.1004844680428505</v>
       </c>
       <c r="JB31" t="n">
         <v>0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.1223552003502846</v>
+        <v>-0.1223606020212173</v>
       </c>
       <c r="JB32" t="n">
         <v>0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.08935345709323883</v>
+        <v>-0.08936537057161331</v>
       </c>
       <c r="JB33" t="n">
         <v>0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.09268514811992645</v>
+        <v>-0.09269715845584869</v>
       </c>
       <c r="JB34" t="n">
         <v>0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.111846387386322</v>
+        <v>-0.1118580996990204</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.1958319842815399</v>
+        <v>-0.1958337873220444</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.3785246610641479</v>
+        <v>-0.3784924745559692</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.3362975418567657</v>
+        <v>-0.3362710773944855</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.2237957119941711</v>
+        <v>-0.223796010017395</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.3872865438461304</v>
+        <v>-0.387248694896698</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.3846061229705811</v>
+        <v>-0.3845561742782593</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.1985444277524948</v>
+        <v>-0.1984011828899384</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.0939415767788887</v>
+        <v>-0.09401106089353561</v>
       </c>
       <c r="JB43" t="n">
         <v>0.4399999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0911637470126152</v>
+        <v>-0.09125158935785294</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.01742114126682281</v>
+        <v>-0.01706576347351074</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0369752012193203</v>
+        <v>-0.03705062344670296</v>
       </c>
       <c r="JB46" t="n">
         <v>0.8599999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.04925280064344406</v>
+        <v>-0.04930358752608299</v>
       </c>
       <c r="JB47" t="n">
         <v>0.8599999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.09719760715961456</v>
+        <v>-0.09725334495306015</v>
       </c>
       <c r="JB48" t="n">
         <v>0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.06005785241723061</v>
+        <v>-0.06009390577673912</v>
       </c>
       <c r="JB49" t="n">
         <v>0.5799999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.1299077272415161</v>
+        <v>-0.1299622654914856</v>
       </c>
       <c r="JB50" t="n">
         <v>0.4399999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.05442016571760178</v>
+        <v>-0.05445978790521622</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.02000000000000007</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.06444395333528519</v>
+        <v>-0.06449407339096069</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.16</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.07186150550842285</v>
+        <v>-0.07189991325139999</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.07350623607635498</v>
+        <v>-0.0735446959733963</v>
       </c>
       <c r="JB54" t="n">
         <v>0.1199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.07482249289751053</v>
+        <v>-0.07488631457090378</v>
       </c>
       <c r="JB55" t="n">
         <v>0.8599999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.05305556207895279</v>
+        <v>-0.05309003219008446</v>
       </c>
       <c r="JB56" t="n">
         <v>0.8599999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.01055753603577614</v>
+        <v>-0.01062330231070518</v>
       </c>
       <c r="JB57" t="n">
         <v>0.8599999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.06269669532775879</v>
+        <v>-0.06276223063468933</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.08061366528272629</v>
+        <v>-0.0806388258934021</v>
       </c>
       <c r="JB59" t="n">
         <v>0.5799999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.08197681605815887</v>
+        <v>-0.08201444149017334</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.1108302623033524</v>
+        <v>-0.1108822822570801</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.06600624322891235</v>
+        <v>-0.06603603810071945</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.16</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.07610226422548294</v>
+        <v>-0.07613519579172134</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.16</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.07568160444498062</v>
+        <v>-0.07574779540300369</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.02000000000000007</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.105487048625946</v>
+        <v>-0.1055164337158203</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.02000000000000007</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.09019684046506882</v>
+        <v>-0.09023639559745789</v>
       </c>
       <c r="JB66" t="n">
         <v>0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.06933597475290298</v>
+        <v>-0.06938204914331436</v>
       </c>
       <c r="JB67" t="n">
         <v>0.5799999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.05440469831228256</v>
+        <v>-0.05444853007793427</v>
       </c>
       <c r="JB68" t="n">
         <v>0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.0867888405919075</v>
+        <v>-0.08682642877101898</v>
       </c>
       <c r="JB69" t="n">
         <v>0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0707964226603508</v>
+        <v>-0.07084301114082336</v>
       </c>
       <c r="JB70" t="n">
         <v>0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.068707175552845</v>
+        <v>-0.06876207143068314</v>
       </c>
       <c r="JB71" t="n">
         <v>0.8599999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.05209867656230927</v>
+        <v>-0.05214268714189529</v>
       </c>
       <c r="JB72" t="n">
         <v>0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.0005612298846244812</v>
+        <v>-0.0006295405328273773</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.0384579598903656</v>
+        <v>-0.03851442784070969</v>
       </c>
       <c r="JB74" t="n">
         <v>0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.0004858933389186859</v>
+        <v>0.0004165768623352051</v>
       </c>
       <c r="JB75" t="n">
         <v>0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.05870705842971802</v>
+        <v>0.0586516484618187</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.05335518717765808</v>
+        <v>0.0532919317483902</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.02700178325176239</v>
+        <v>0.02693681418895721</v>
       </c>
       <c r="JB78" t="n">
         <v>0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.04470343887805939</v>
+        <v>0.04464441537857056</v>
       </c>
       <c r="JB79" t="n">
         <v>0.2599999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.04987965524196625</v>
+        <v>0.04982466995716095</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.04540020227432251</v>
+        <v>0.04534105211496353</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.02000000000000007</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.04811068624258041</v>
+        <v>0.04804564267396927</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.007467985153198242</v>
+        <v>0.007407203316688538</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.16</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.05457887053489685</v>
+        <v>0.05451789498329163</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.16</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.04480016231536865</v>
+        <v>0.04473885148763657</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.04498902708292007</v>
+        <v>0.04493612796068192</v>
       </c>
       <c r="JB86" t="n">
         <v>0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.05411030352115631</v>
+        <v>0.05405670404434204</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.16</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.0279642716050148</v>
+        <v>0.02789328247308731</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.03396087884902954</v>
+        <v>-0.0340256541967392</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.05659492313861847</v>
+        <v>-0.05661942437291145</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.03630799055099487</v>
+        <v>0.03623915463685989</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.03796381503343582</v>
+        <v>0.0378936231136322</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.04701521992683411</v>
+        <v>-0.04706629365682602</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.1600000000000001</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.04896462708711624</v>
+        <v>0.0489012822508812</v>
       </c>
       <c r="JB94" t="n">
         <v>0.5799999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.04587066173553467</v>
+        <v>0.04582375288009644</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.05391864478588104</v>
+        <v>0.05385996401309967</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.03807695955038071</v>
+        <v>-0.03813020139932632</v>
       </c>
       <c r="JB97" t="n">
         <v>0.5799999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.04818764328956604</v>
+        <v>0.04812697321176529</v>
       </c>
       <c r="JB98" t="n">
         <v>0.5799999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.03586387634277344</v>
+        <v>0.0358087569475174</v>
       </c>
       <c r="JB99" t="n">
         <v>0.3</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.05076360702514648</v>
+        <v>0.05070539563894272</v>
       </c>
       <c r="JB100" t="n">
         <v>0.5799999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.00429101288318634</v>
+        <v>0.004236370325088501</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.1600000000000001</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.05323886126279831</v>
+        <v>0.05318965017795563</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.04348328709602356</v>
+        <v>0.04342278838157654</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.02488206326961517</v>
+        <v>0.02482476830482483</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.16</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.04688750207424164</v>
+        <v>0.04683145880699158</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.03479583561420441</v>
+        <v>0.03473842144012451</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.16</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.03747621178627014</v>
+        <v>0.03742241859436035</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.02000000000000007</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.04493261873722076</v>
+        <v>0.04488348960876465</v>
       </c>
       <c r="JB108" t="n">
         <v>0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.04749457538127899</v>
+        <v>0.04744386672973633</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.04194782674312592</v>
+        <v>0.04189611971378326</v>
       </c>
       <c r="JB110" t="n">
         <v>0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.05188500136137009</v>
+        <v>0.05183067917823792</v>
       </c>
       <c r="JB111" t="n">
         <v>0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.0249738022685051</v>
+        <v>0.02491670101881027</v>
       </c>
       <c r="JB112" t="n">
         <v>0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.04779352247714996</v>
+        <v>0.04773968458175659</v>
       </c>
       <c r="JB113" t="n">
         <v>0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.03729608654975891</v>
+        <v>0.03724227100610733</v>
       </c>
       <c r="JB114" t="n">
         <v>0.5799999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.04784089326858521</v>
+        <v>0.04778749495744705</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.02761418372392654</v>
+        <v>0.02754560112953186</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.08415214717388153</v>
+        <v>-0.08417674899101257</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.5799999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.09932079166173935</v>
+        <v>-0.09937569499015808</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.02543231844902039</v>
+        <v>-0.02545581385493279</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.1033344939351082</v>
+        <v>-0.1033812612295151</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.04053862392902374</v>
+        <v>-0.04056995362043381</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.05571398138999939</v>
+        <v>-0.05575939267873764</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.03743407875299454</v>
+        <v>-0.037492286413908</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.9999999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.05488412827253342</v>
+        <v>-0.05492998659610748</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.9999999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.01704306527972221</v>
+        <v>-0.01710879057645798</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.9999999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.1478634625673294</v>
+        <v>-0.1478793174028397</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.9999999999999996</v>
